--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/facturacionManual.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/facturacionManual.xlsx
@@ -79,43 +79,43 @@
     <t>ARIDOS Y CONSTRUCCION DEMO SPA</t>
   </si>
   <si>
-    <t>314792791</t>
-  </si>
-  <si>
-    <t>315822266</t>
-  </si>
-  <si>
-    <t>31693092K</t>
-  </si>
-  <si>
-    <t>317247684</t>
-  </si>
-  <si>
-    <t>317643630</t>
-  </si>
-  <si>
-    <t>319069052</t>
-  </si>
-  <si>
-    <t>31954419K</t>
-  </si>
-  <si>
-    <t>31986095K</t>
-  </si>
-  <si>
-    <t>32017771K</t>
-  </si>
-  <si>
-    <t>320573662</t>
-  </si>
-  <si>
-    <t>32104880K</t>
-  </si>
-  <si>
-    <t>321365568</t>
-  </si>
-  <si>
-    <t>322078279</t>
+    <t>760389102</t>
+  </si>
+  <si>
+    <t>76464462K</t>
+  </si>
+  <si>
+    <t>769601902</t>
+  </si>
+  <si>
+    <t>770549221</t>
+  </si>
+  <si>
+    <t>772902824</t>
+  </si>
+  <si>
+    <t>77918675K</t>
+  </si>
+  <si>
+    <t>780098686</t>
+  </si>
+  <si>
+    <t>780635517</t>
+  </si>
+  <si>
+    <t>781467405</t>
+  </si>
+  <si>
+    <t>784015270</t>
+  </si>
+  <si>
+    <t>784579840</t>
+  </si>
+  <si>
+    <t>785087658</t>
+  </si>
+  <si>
+    <t>786650968</t>
   </si>
   <si>
     <t>OC</t>
